--- a/AAII_Financials/Quarterly/ADI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ADI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>ADI</t>
   </si>
@@ -656,516 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
         <v>46144</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43589</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43498</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43407</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43316</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43225</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43134</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4021900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3623500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3160300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3076100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2880300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2640100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2423200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2443200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2312200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2159000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2512700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2716500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3076500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3262900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3249600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3247700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3109900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2972100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2684300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2339600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1758900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1661400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1558500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1526300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1456100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1317100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1443200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1480100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3067700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1541100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1536100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1558200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3130400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1566900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1541200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1433900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2132400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>984400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1003600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1314400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1183700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1115300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1134300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1090600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1028500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>992900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1027100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1001000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>979000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1038800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1069800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1114900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1118400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1125300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1104900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1066700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1027500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1282300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1217700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>537700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>524800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>513100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>503200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>483600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>470400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>455400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>501000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>482300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>994000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>501400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>490400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>497600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>986300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>495200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>535100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>667300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>843500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>335900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>336900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2707500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2439800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2045000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1941800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1789700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1611600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1430300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1416100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1311200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1180000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1473900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1646700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1961600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2144500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2124300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2142800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2043200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1944600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1402000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1121900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1221200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1136600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1045400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1023100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>972500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>846700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>848200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>942200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>997800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2073700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1039700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1045700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1060600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2144100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1071700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1006100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>766600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1288900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>648500</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>666700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,130 +1220,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>533500</v>
+      </c>
+      <c r="E12" s="3">
         <v>509300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>467400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>467000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>454300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>441800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>402900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>378900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>362700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>354900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>391400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>406600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>423800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>415800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>414100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>421000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>431800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>420900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>426800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>399100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>306600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>302200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>288200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>280200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>260800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>252400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>257100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>277000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>280100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>573200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>287400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>295300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>291600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>578100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>288600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>273700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>275700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>419200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>184000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>172900</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1452,130 +1468,136 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>48000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>63900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>114000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>196800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>138200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>46700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>59700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>384100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>9400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>19100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>11100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>64800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>29900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>21800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>58400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>57300</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
         <v>0</v>
       </c>
       <c r="AN14" s="3">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3">
         <v>49500</v>
       </c>
       <c r="AP14" s="3">
+        <v>49500</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1583,10 +1605,10 @@
         <v>188000</v>
       </c>
       <c r="E15" s="3">
+        <v>188000</v>
+      </c>
+      <c r="F15" s="3">
         <v>187300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>187400</v>
       </c>
       <c r="G15" s="3">
         <v>187400</v>
@@ -1598,64 +1620,64 @@
         <v>187400</v>
       </c>
       <c r="J15" s="3">
-        <v>187800</v>
+        <v>187400</v>
       </c>
       <c r="K15" s="3">
         <v>187800</v>
       </c>
       <c r="L15" s="3">
+        <v>187800</v>
+      </c>
+      <c r="M15" s="3">
         <v>188900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>190300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>202700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>250700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>253000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>253100</v>
-      </c>
-      <c r="R15" s="3">
-        <v>252900</v>
       </c>
       <c r="S15" s="3">
         <v>252900</v>
       </c>
       <c r="T15" s="3">
+        <v>252900</v>
+      </c>
+      <c r="U15" s="3">
         <v>253500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>253400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>213600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>107800</v>
       </c>
       <c r="X15" s="3">
         <v>107800</v>
       </c>
       <c r="Y15" s="3">
+        <v>107800</v>
+      </c>
+      <c r="Z15" s="3">
         <v>107600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>108000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>107100</v>
       </c>
       <c r="AB15" s="3">
         <v>107100</v>
       </c>
       <c r="AC15" s="3">
-        <v>107200</v>
+        <v>107100</v>
       </c>
       <c r="AD15" s="3">
         <v>107200</v>
@@ -1664,40 +1686,43 @@
         <v>107200</v>
       </c>
       <c r="AF15" s="3">
+        <v>107200</v>
+      </c>
+      <c r="AG15" s="3">
         <v>214600</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>107300</v>
       </c>
       <c r="AH15" s="3">
         <v>107300</v>
       </c>
       <c r="AI15" s="3">
+        <v>107300</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>107400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>214100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>107000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>98300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>112200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>86900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>18200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>17900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2433100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2243800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2115300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2137900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2058000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1960400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1868000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1877600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1808600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1766900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1910600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1972900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2123500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2111400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2118800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2145200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2216600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2053900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2319500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2455700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1149200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1141700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1094600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1064600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1037000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>973000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1030100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1104900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1033400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2142200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1085300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1069900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1069200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2186000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1125000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1093000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1239100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1720300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>718200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>646600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1588800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1379700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1045000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>938300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>822400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>679700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>555200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>565600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>503600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>392100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>602100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>743600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>953000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1151500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1130800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1102500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>893300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>918200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>364800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-116100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>609700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>519700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>463900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>461700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>419100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>344100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>273500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>338300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>446700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>925500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>455800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>466200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>489000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>944400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>441900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>448200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>194800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>412100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>266200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2025,618 +2057,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>14600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>5100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>22200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>9700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1773000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1571900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1235300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1129800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1007700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>868100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>738700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>761800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>681800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>581400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>787900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>951100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1209600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1414800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1721400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1668300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1478100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1504900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>945300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>377400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>813100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>717200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>680500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>668100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>620400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>548400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>479000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>543800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>653600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1328700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>659300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>669600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>692000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1346300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>641800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>634900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>402300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>626100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>330200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E22" s="3">
         <v>87600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>86300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>88200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>79600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>74700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>75300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>82800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>77100</v>
       </c>
       <c r="M22" s="3">
         <v>77100</v>
       </c>
       <c r="N22" s="3">
+        <v>77100</v>
+      </c>
+      <c r="O22" s="3">
         <v>71600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>69300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>63300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>60500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>51200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>49500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>52000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>54600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>44700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>43100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>42500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>48600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>50000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>48800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>50800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>59900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>118400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>58700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>59100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>61700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>132800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>68000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>63500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>73100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>114300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>42600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1545900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1324800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>945900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>887200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>763400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>625900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>435600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>516300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>423000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>324600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>513400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>571800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>874800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1087900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1073500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1048000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>847900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>879200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>323600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-156200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>572300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>476000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>436600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>417300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>373000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>295100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>226200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>287800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>389600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>808300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>399900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>409300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>430500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>815500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>375300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>381700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>126800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>320000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>233300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>323400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>205800</v>
+      </c>
+      <c r="E24" s="3">
         <v>148500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>115000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>99500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>244900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>44300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>38300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>30800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>50700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>73400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>110300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>112000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>111800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>99000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>96000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-231900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>69000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>53100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>48100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>30800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>10400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>27400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>22300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>27200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>85400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>37400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-49500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>121900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>82100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>34000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>57900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>9300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>16200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1340100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1176400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>830800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>787700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>518500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>569800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>391300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>478100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>392200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>302200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>462700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>498400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>877000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>977700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>961500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>936200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>749000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>783300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>280100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>75700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>503300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>422900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>388500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>386500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>362700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>267700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>203900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>277700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>362400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>722900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>362500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>458900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>408600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>693600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>293200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>347700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>68900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>310700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>217100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1340100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1176400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>830800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>787700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>518500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>569800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>391300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>478100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>392200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>302200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>462700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>498400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>877000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>977700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>961500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>936200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>749000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>783300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>280100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>75700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>503300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>422900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>388500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>386500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>362700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>267700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>203900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>277200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>361600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>721000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>361500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>457400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>407000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>690700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>292000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>346400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>67900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>310700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>217000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3167,8 +3227,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
@@ -3176,8 +3236,8 @@
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -3194,8 +3254,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -3215,23 +3275,23 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-54000</v>
       </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="AJ29" s="3">
-        <v>-47400</v>
       </c>
       <c r="AK29" s="3">
         <v>-47400</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
+      <c r="AL29" s="3">
+        <v>-47400</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3245,8 +3305,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,252 +3555,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-14600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-22200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-9700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1340100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1176400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>830800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>787700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>518500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>569800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>391300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>478100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>392200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>302200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>462700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>498400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>877000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>977700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>961500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>936200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>749000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>783300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>280100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>75700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>503300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>422900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>388500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>386500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>362700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>267700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>203900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>277200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>361600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>721000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>354000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>403400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>407000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>643300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>244600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>346400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>67900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>310700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>217000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1340100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1176400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>830800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>787700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>518500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>569800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>391300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>478100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>392200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>302200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>462700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>498400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>877000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>977700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>961500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>936200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>749000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>783300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>280100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>75700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>503300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>422900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>388500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>386500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>362700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>267700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>203900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>277200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>361600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>721000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>354000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>403400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>407000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>643300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>244600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>346400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>67900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>310700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>217000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
         <v>46144</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43589</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43498</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43407</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43316</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43225</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43134</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,163 +4277,167 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2165900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2436900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2905900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2499400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2321200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2376200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2350000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1991300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2106000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1939700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1303600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>958100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1149200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1177600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1670500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1470600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1525000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1737700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1790400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1978000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1480700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1305200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1048100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1055900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1090300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>784900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>654400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>648300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>612200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>713600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>605900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>816600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>772600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>806500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>827600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1047800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>908600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5697700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4987300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>921100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1002400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1143000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1152900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1148100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>371500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>371800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>439700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>424100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4358,14 +4447,14 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>24</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -4418,514 +4507,529 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AL42" s="3">
-        <v>0</v>
-      </c>
       <c r="AM42" s="3">
         <v>0</v>
       </c>
       <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
         <v>490600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1329800</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>3134700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2389600</v>
+      </c>
+      <c r="E43" s="3">
         <v>2051700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1360200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1436100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1553300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1382400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1192400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1336300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1127200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1004600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1196700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1469700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1616200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1616300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1629900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1800500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1742600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1608300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1636900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1459100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>823200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>814100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>827000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>737500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>681700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>588200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>584400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>635100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>690000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>686000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>713700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>639700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>710800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>759600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>709800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>689000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>692600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>630400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>472500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>477600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1931500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1848400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1767100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1656300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1596900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1524900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1474700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1447700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1427900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1479100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1553200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1642200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1709300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1648100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1522900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1399900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1203400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1075300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>972600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1200600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>657500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>641200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>618600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>608300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>612600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>590300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>588500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>609900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>638300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>608100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>593200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>586800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>563600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>551200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>559700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>550800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>519700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>647900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>365600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>376600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E45" s="3">
         <v>6500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>60900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>338200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>267000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>218700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>212900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>236800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>740700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>129100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>142200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>131100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>116000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>100600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>87800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>83900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>91800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>66600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>72800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>72400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>134900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>69600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>71000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>80700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>63700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>67800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>68900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>78600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7072500</v>
+      </c>
+      <c r="E46" s="3">
         <v>7809800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7602500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7108100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6924600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5588500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5733100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5484700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5442900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5193600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4415900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4384000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4835200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4744900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5161500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4938000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4689700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4634200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4636700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5378300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3090500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2902800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2624700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2517700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2485200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2051300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1911200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1985100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2007100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2080500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1985200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2112100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2116600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2188300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2177700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2351300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2188600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7535500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>7233700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4974900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4971,11 +5075,11 @@
       <c r="Q47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" s="3">
         <v>122300</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>24</v>
@@ -4983,315 +5087,324 @@
       <c r="U47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W47" s="3">
         <v>127900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>105600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>94000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>91700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>86700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>83000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>76000</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>30200</v>
       </c>
       <c r="AD47" s="3">
         <v>30200</v>
       </c>
       <c r="AE47" s="3">
+        <v>30200</v>
+      </c>
+      <c r="AF47" s="3">
         <v>32300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>31600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>34800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>28700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>28500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>27000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>26200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>24800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>29000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>28500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>23000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3352000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3292300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3249000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3545200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3299300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3336100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3355200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3658100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3395700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3415200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3281900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3496400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2922800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2742000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2524700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2401300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2180000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2094100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2037300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1979100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1173700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1160600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1129200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1377200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1381600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1433000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1436000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1220000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1221200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1211500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1181700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1154300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1108000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1114600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1115400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1107300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1098800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1089300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>628900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>636100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35457000</v>
+      </c>
+      <c r="E49" s="3">
         <v>34228500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34574400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34959000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>35347800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35732600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>36128200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>36495200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>36907500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>37344600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37784200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>38225100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>38675800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>39174800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>39676400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>40178500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>40684800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>41182500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>41703300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>42185600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>15527700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>15676000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15818200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15928700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>16070700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>16182600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>16330100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>16474100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>16594300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>16739600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>16885600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>21809000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>17174900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>17324400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>17406500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>17536900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>17682500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>17857400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2206900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2228500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,130 +5650,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E52" s="3">
         <v>888900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>805700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>513300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>695500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>701700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>718300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>506500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>766800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>762200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>734300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>465700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>688100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>634100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2872000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2662200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2791600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2889800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2838300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2651200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1743800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1754800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1776200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1558300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1579100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1608000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1669200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1683300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1711800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1713200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1741000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>112400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>120600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>122200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>127400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>120900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>116000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>112000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>110800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48424400</v>
+      </c>
+      <c r="E54" s="3">
         <v>47949100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47991200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47992700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48192600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47344500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47967500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>48228300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48618400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48861900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48388500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>48794500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>49346700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49544700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>50234500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>50302400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>50346200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>50800700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>51215600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>52322100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21641200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21588200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21440100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21468600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21599600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21350900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21376800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21392600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>21566700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>21776300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>21828300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>20438400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>20548600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>20776500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>20853300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>21141300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>21115000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>26622700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10203400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>7970300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,178 +6117,182 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>682200</v>
+      </c>
+      <c r="E57" s="3">
         <v>598600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>549100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>543800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>490700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>429400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>368900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>487500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>424700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>422700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>398100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>493000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>585600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>569000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>534700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>582200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>545100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>451400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>436200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>443400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>265900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>279200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>227400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>227300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>215900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>194200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>211700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>225300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>220200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>208200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>222600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>260900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>215700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>213300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>223100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>236600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>228100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>190200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>156700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>171400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2392400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1473300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1460800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>532100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>566100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>570600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1000400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1052400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1462600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1507400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1080800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1192600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>590300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>255500</v>
       </c>
-      <c r="Q58" s="3" t="s">
+      <c r="R58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -6170,558 +6303,573 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>516700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1324700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1324500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>399200</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>449300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>448900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>748500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>299700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>411400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>374200</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
       <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
         <v>67000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>56000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>50000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>300000</v>
       </c>
-      <c r="AM58" s="3" t="s">
+      <c r="AN58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4321200</v>
       </c>
-      <c r="AO58" s="3" t="s">
+      <c r="AP58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>479400</v>
+      </c>
+      <c r="E59" s="3">
         <v>349000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>791700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1436300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>494900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>385300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>564900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1003800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>404300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>369700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>414700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>991200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>423400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>309000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1899000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1860500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1896100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1874800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1785700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1810200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1202700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1173200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1050100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1137700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1022600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>938800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>810400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>983700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>852000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>782600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>627400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1211200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1100700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1163600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>963400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1059700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>873000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>937900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>655000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>611500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5656300</v>
+      </c>
+      <c r="E60" s="3">
         <v>4456900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4330600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3245800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2979000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2690600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2971000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2988300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3226600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3297300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2923400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3201000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2831000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2646400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2433700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2442700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2441200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2326200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2221900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2770300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2793300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2776800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1676800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1687800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1582000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1770500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1508600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1483700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1365000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>850000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1051700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1338900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1432900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1236500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1596300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1101100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5449300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>811600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>782900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6771600</v>
+      </c>
+      <c r="E61" s="3">
         <v>7235400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7240300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8429000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8139900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6648400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6618600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6952900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6655700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6611700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5946700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6262900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6437700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6475600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6543300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6548600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6252800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6253200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6253600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6253200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3824800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3823600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4747300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5145100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5143700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5142200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4745300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5192300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5278600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5612400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6234500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6265700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6532700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6926400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7384900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7551100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>8199200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8572400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3805400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1732200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>607700</v>
+      </c>
+      <c r="E62" s="3">
         <v>608600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>637200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>228600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>616200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>615200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>792600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>379400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>802900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>816100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>994500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>561600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1023600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1084100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4726100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4845700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5013500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5121400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5312800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5306000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2759100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2820700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2928300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2960600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2990600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3035900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3171500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2982600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3014100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3056700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3158400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1852800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1820800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1831800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1884100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1832300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1891800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2634400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>279900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>289500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14873500</v>
+      </c>
+      <c r="E66" s="3">
         <v>14207100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14203900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14177000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14106800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12333900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12897000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13052000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13428300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13613100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12840400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13229400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13443000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13531500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13703000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13837000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13707600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13700900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13788300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14329500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9377200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9421100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9352400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9470700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9822000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9760100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9687300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9683500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9776400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10034100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10242800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9170200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9692400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10191100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10505500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>10979800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>11192100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>16656100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4896900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2804700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,8 +7660,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7618,8 +7785,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12330800</v>
+      </c>
+      <c r="E72" s="3">
         <v>11526000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10886100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10539500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10238700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10210300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10131600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10196600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10175300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10239500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10393400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10356800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10286400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9839800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9297300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8721300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8175400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7820500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7434700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7517300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7812900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7564100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7395600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7236200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7079300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6945400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6906300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6899300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6821800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6659400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6491000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5982700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5449500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5213900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5012400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4910900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4730100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4827500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4873200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4785800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33550900</v>
+      </c>
+      <c r="E76" s="3">
         <v>33742000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33787300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>33815800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>34085800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35010600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35070500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>35176300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>35190100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>35248800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>35548100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>35565100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>35903700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>36013200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>36531500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>36465300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>36638600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>37099800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>37427300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>37992500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12264000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12167100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12087700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11997900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11777600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11590900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11689500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11709200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11790200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11742300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11585400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11268200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10856200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10585400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10347800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10161500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9922900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9966600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5306400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5165600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
         <v>46144</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43589</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43498</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43407</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43316</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43225</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43134</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1340100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1176400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>830800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>787700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>518500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>569800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>391300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>478100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>392200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>302200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>462700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>498400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>877000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>977700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>961500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>936200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>749000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>783300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>280100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>75700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>503300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>422900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>388500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>386500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>362700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>267700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>203900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>277200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>361600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>721000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>354000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>403400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>407000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>643300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>244600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>346400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>67900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>310700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>217000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E83" s="3">
         <v>100300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>98400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>97200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>92400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>88800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>84300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>82900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>86200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>85300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>70700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>587500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>572600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>579000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>576100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>569800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>479000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>196200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>198200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>201400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>202200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>201500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>203300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>203900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>205200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>204100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>402000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>200600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>201200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>199900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>398000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>198500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>189700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>202500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>191900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>54300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E89" s="3">
         <v>872000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1368500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1700800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1165100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>819500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1126800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1050800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>855000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>807900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1138800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1187300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1142500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1081600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1406300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1149300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1247800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1221800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>856400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>940700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>630000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>736400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>427900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>672600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>557200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>429000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>349600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>657900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>552500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1042600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>371800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>714400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>620700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>388700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>610700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-360000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>861900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>322600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>487000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-145700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-137700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-109300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-215200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-79200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-90300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-149000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-165400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-153900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-188200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-223000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-476400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-324600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-284300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-176200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-304500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-164900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-118800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-111100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-130800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-63800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-59200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-67400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-60200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-54800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-166200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-86000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-51800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-117100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-63200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-65200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-63600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-150500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-41200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-714900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-51900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-107000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-225300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1230100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>328200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-194300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-111600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-172100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-602100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-219100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-479100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-326700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-284500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-176100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-306300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-134100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-113600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-103300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2326800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-47500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-60700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-75100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-61600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-54700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-63800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-58600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-170800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-96200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-89000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-54500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-170500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-64500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>426100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-7031000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>1769800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-556900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,130 +10427,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>535300</v>
+      </c>
+      <c r="E96" s="3">
         <v>536500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>484300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>486900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>490200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>491000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>456300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>456800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>456500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>456100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>426100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>428000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>430500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>435200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-385500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-390300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-394000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-397500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-362600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-371200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-254500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-254400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-229200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-229600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-228800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-228600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-199200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-200200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-200100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-377200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-177700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-179400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-178900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-166700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-166900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-166300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-129700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-129600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,130 +10925,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1160100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1289100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-855000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1297300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1121400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-573900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1053900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-516600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>430400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-574200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-899400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-844100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1289900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1030400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-886900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1318400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1148200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-937300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2769700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-406600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-419600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-363800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-676200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-219200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-235700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-289600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-557100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-594600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-975100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-486100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-580700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-599100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1178200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-548000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-490100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-4853000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>10971700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1982600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-111400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10840,213 +11088,219 @@
       <c r="M101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O101" s="3">
         <v>-10500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-10500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-12700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>2000</v>
       </c>
-      <c r="AN101" s="3">
-        <v>0</v>
-      </c>
       <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-271000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-468900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>406500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>178200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-55000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>358700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-114700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>166300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>636100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>345500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-191200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-492900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>199900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-54400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-212800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-52700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-187600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>497300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>175500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>257200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-34400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>305300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>130500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>36200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-101400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-103000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-210700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>44000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-33900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-241300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-220300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>139300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-4789200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4776600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>4066100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-182500</v>
       </c>
     </row>
